--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260814.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260814.xlsx
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>5,443,520</t>
+          <t>2,056,288</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2,056,288</t>
+          <t>5,443,520</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>594,000</t>
+          <t>386,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,058,587</t>
+          <t>594,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>386,000</t>
+          <t>2,058,587</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,311,000</t>
+          <t>5,878,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>5,878,000</t>
+          <t>3,311,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,229,441</t>
+          <t>3,575,981</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,575,981</t>
+          <t>1,229,441</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>2,668,703</t>
+          <t>4,576,578</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>4,576,578</t>
+          <t>2,668,703</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,218,076</t>
+          <t>2,250,107</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2,250,107</t>
+          <t>1,218,076</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>187,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>187,000</t>
+          <t>96,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>96,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>5,096,956</t>
+          <t>797,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>827,000</t>
+          <t>5,096,956</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>797,000</t>
+          <t>827,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>234,000</t>
+          <t>511,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,603,400</t>
+          <t>234,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>511,000</t>
+          <t>1,603,400</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,030,121</t>
+          <t>118,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,806,000</t>
+          <t>1,030,121</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>118,000</t>
+          <t>1,806,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>340,000</t>
+          <t>67,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>67,538</t>
+          <t>340,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>261,000</t>
+          <t>161,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>161,000</t>
+          <t>699,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>699,000</t>
+          <t>261,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>118,000</t>
+          <t>73,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>73,000</t>
+          <t>345,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2207,17 +2207,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>345,000</t>
+          <t>118,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
